--- a/Figure 6/Figure 6-I.xlsx
+++ b/Figure 6/Figure 6-I.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B1B888-816E-4BFF-A5F6-9C4D5EC677E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57927CDA-FCC3-4B34-BF87-60E72C865138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20310" yWindow="2470" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +106,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,8 +134,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -417,103 +424,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1.8733075580695631</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1.1899908725139881</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.80085299017260358</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>1.115749219453932</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.76424303035813168</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>0.53873079370851895</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>1.1042674930345218</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>0.77592381356606621</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>0.81670386806073991</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>1.6058027739436787</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>0.94034729915735049</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>0.97461140766106025</v>
       </c>
     </row>
